--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EA8A870-CE18-4FB6-B6B7-C18FACFDC945}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEB5436A-92ED-42E3-92E8-5AA746CA0E8F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -213,7 +213,7 @@
     <t>High</t>
   </si>
   <si>
-    <t xml:space="preserve"> no feeling good</t>
+    <t>Feeling good and energetic.</t>
   </si>
 </sst>
 </file>
@@ -1044,36 +1044,36 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="B7" s="14">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="C7" s="14">
+        <v>30</v>
+      </c>
+      <c r="D7" s="14">
+        <v>120</v>
+      </c>
+      <c r="E7" s="14">
         <v>60</v>
       </c>
-      <c r="D7" s="14">
-        <v>180</v>
-      </c>
-      <c r="E7" s="14">
-        <v>150</v>
-      </c>
       <c r="F7" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G7" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H7" s="14">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v>950</v>
+        <v>635</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v>490</v>
+        <v>805</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>49</v>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEB5436A-92ED-42E3-92E8-5AA746CA0E8F}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38A5832B-F813-4B26-8C7E-A4D5173123AA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -214,6 +214,18 @@
   </si>
   <si>
     <t>Feeling good and energetic.</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>depressed because of career related tension and  confusion.</t>
   </si>
 </sst>
 </file>
@@ -1059,7 +1071,7 @@
         <v>60</v>
       </c>
       <c r="F7" s="14">
-        <v>5</v>
+        <v>250</v>
       </c>
       <c r="G7" s="14">
         <v>5</v>
@@ -1069,11 +1081,11 @@
       </c>
       <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v>635</v>
+        <v>880</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v>805</v>
+        <v>560</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>49</v>
@@ -1088,27 +1100,51 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+    <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B8" s="14">
+        <v>540</v>
+      </c>
+      <c r="C8" s="14">
+        <v>0</v>
+      </c>
+      <c r="D8" s="14">
+        <v>90</v>
+      </c>
+      <c r="E8" s="14">
+        <v>60</v>
+      </c>
+      <c r="F8" s="14">
+        <v>200</v>
+      </c>
+      <c r="G8" s="14">
+        <v>4</v>
+      </c>
+      <c r="H8" s="14">
+        <v>60</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38A5832B-F813-4B26-8C7E-A4D5173123AA}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6578672-107F-491F-BACD-AEFE4FFA6119}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -226,6 +226,12 @@
   </si>
   <si>
     <t>depressed because of career related tension and  confusion.</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not feel happy and not feel sad, just feeling normal. </t>
   </si>
 </sst>
 </file>
@@ -1146,27 +1152,51 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+    <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
+        <v>59402</v>
+      </c>
+      <c r="B9" s="14">
+        <v>460</v>
+      </c>
+      <c r="C9" s="14">
+        <v>30</v>
+      </c>
+      <c r="D9" s="14">
+        <v>120</v>
+      </c>
+      <c r="E9" s="14">
+        <v>90</v>
+      </c>
+      <c r="F9" s="14">
+        <v>420</v>
+      </c>
+      <c r="G9" s="14">
+        <v>7</v>
+      </c>
+      <c r="H9" s="14">
+        <v>30</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6578672-107F-491F-BACD-AEFE4FFA6119}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A7D3317-EF23-4A10-AAB9-5327EF25D9DD}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4920" yWindow="2652" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="13">
-        <v>59402</v>
+        <v>46253</v>
       </c>
       <c r="B9" s="14">
         <v>460</v>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A7D3317-EF23-4A10-AAB9-5327EF25D9DD}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DCE91DB-253A-41BF-A894-6102DCFB9A22}"/>
   <bookViews>
-    <workbookView xWindow="4920" yWindow="2652" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,6 +232,9 @@
   </si>
   <si>
     <t xml:space="preserve">not feel happy and not feel sad, just feeling normal. </t>
+  </si>
+  <si>
+    <t>feeling neutral.</t>
   </si>
 </sst>
 </file>
@@ -1199,26 +1202,50 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B10" s="14">
+        <v>500</v>
+      </c>
+      <c r="C10" s="14">
+        <v>40</v>
+      </c>
+      <c r="D10" s="14">
+        <v>90</v>
+      </c>
+      <c r="E10" s="14">
+        <v>90</v>
+      </c>
+      <c r="F10" s="14">
+        <v>250</v>
+      </c>
+      <c r="G10" s="14">
+        <v>5</v>
+      </c>
+      <c r="H10" s="14">
+        <v>60</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DCE91DB-253A-41BF-A894-6102DCFB9A22}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{035F26E6-EED6-45DF-ABC8-501A13AE55B5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -235,6 +235,9 @@
   </si>
   <si>
     <t>feeling neutral.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feeling good . </t>
   </si>
 </sst>
 </file>
@@ -1248,26 +1251,50 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B11" s="14">
+        <v>420</v>
+      </c>
+      <c r="C11" s="14">
+        <v>20</v>
+      </c>
+      <c r="D11" s="14">
+        <v>90</v>
+      </c>
+      <c r="E11" s="14">
+        <v>60</v>
+      </c>
+      <c r="F11" s="14">
+        <v>250</v>
+      </c>
+      <c r="G11" s="14">
+        <v>5</v>
+      </c>
+      <c r="H11" s="14">
+        <v>30</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{035F26E6-EED6-45DF-ABC8-501A13AE55B5}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D57FDBC-ED93-46EE-BB03-37F7574B2233}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1297,26 +1297,50 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B12" s="14">
+        <v>500</v>
+      </c>
+      <c r="C12" s="14">
+        <v>40</v>
+      </c>
+      <c r="D12" s="14">
+        <v>150</v>
+      </c>
+      <c r="E12" s="14">
+        <v>120</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
+        <v>60</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="93" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D57FDBC-ED93-46EE-BB03-37F7574B2233}"/>
+  <xr:revisionPtr revIDLastSave="106" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE0529D4-9C58-47E1-B14E-B420C63AE2CA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -238,6 +238,15 @@
   </si>
   <si>
     <t xml:space="preserve">feeling good . </t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>good and energetic.</t>
   </si>
 </sst>
 </file>
@@ -1343,26 +1352,50 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B13" s="14">
+        <v>540</v>
+      </c>
+      <c r="C13" s="14">
+        <v>30</v>
+      </c>
+      <c r="D13" s="14">
+        <v>180</v>
+      </c>
+      <c r="E13" s="14">
+        <v>60</v>
+      </c>
+      <c r="F13" s="14">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14">
+        <v>90</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="106" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE0529D4-9C58-47E1-B14E-B420C63AE2CA}"/>
+  <xr:revisionPtr revIDLastSave="136" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EA26761-A138-4B0F-9E82-2E79EA151B69}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -247,6 +247,12 @@
   </si>
   <si>
     <t>good and energetic.</t>
+  </si>
+  <si>
+    <t>feeling good.</t>
+  </si>
+  <si>
+    <t>neutral.</t>
   </si>
 </sst>
 </file>
@@ -1398,48 +1404,96 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B14" s="14">
+        <v>550</v>
+      </c>
+      <c r="C14" s="14">
+        <v>30</v>
+      </c>
+      <c r="D14" s="14">
+        <v>180</v>
+      </c>
+      <c r="E14" s="14">
+        <v>90</v>
+      </c>
+      <c r="F14" s="14">
+        <v>100</v>
+      </c>
+      <c r="G14" s="14">
+        <v>2</v>
+      </c>
+      <c r="H14" s="14">
+        <v>40</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B15" s="14">
+        <v>420</v>
+      </c>
+      <c r="C15" s="14">
+        <v>0</v>
+      </c>
+      <c r="D15" s="14">
+        <v>180</v>
+      </c>
+      <c r="E15" s="14">
+        <v>120</v>
+      </c>
+      <c r="F15" s="14">
+        <v>300</v>
+      </c>
+      <c r="G15" s="14">
+        <v>6</v>
+      </c>
+      <c r="H15" s="14">
+        <v>30</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="136" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EA26761-A138-4B0F-9E82-2E79EA151B69}"/>
+  <xr:revisionPtr revIDLastSave="150" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B15E14F-D812-466B-BE59-DA4D87215311}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>neutral.</t>
+  </si>
+  <si>
+    <t>feeling low.</t>
   </si>
 </sst>
 </file>
@@ -1190,7 +1193,7 @@
         <v>90</v>
       </c>
       <c r="F9" s="14">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="G9" s="14">
         <v>7</v>
@@ -1200,11 +1203,11 @@
       </c>
       <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v>1150</v>
+        <v>1080</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>290</v>
+        <v>360</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>63</v>
@@ -1496,26 +1499,50 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B16" s="14">
+        <v>360</v>
+      </c>
+      <c r="C16" s="14">
+        <v>0</v>
+      </c>
+      <c r="D16" s="14">
+        <v>120</v>
+      </c>
+      <c r="E16" s="14">
+        <v>120</v>
+      </c>
+      <c r="F16" s="14">
+        <v>400</v>
+      </c>
+      <c r="G16" s="14">
+        <v>8</v>
+      </c>
+      <c r="H16" s="14">
+        <v>0</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>440</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="150" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B15E14F-D812-466B-BE59-DA4D87215311}"/>
+  <xr:revisionPtr revIDLastSave="164" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEFD7DC6-D894-4955-A688-AA60DAC7F516}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -256,6 +256,9 @@
   </si>
   <si>
     <t>feeling low.</t>
+  </si>
+  <si>
+    <t>due to continuous classes felling tired.</t>
   </si>
 </sst>
 </file>
@@ -1544,27 +1547,51 @@
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+    <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B17" s="14">
+        <v>420</v>
+      </c>
+      <c r="C17" s="14">
+        <v>20</v>
+      </c>
+      <c r="D17" s="14">
+        <v>180</v>
+      </c>
+      <c r="E17" s="14">
+        <v>120</v>
+      </c>
+      <c r="F17" s="14">
+        <v>250</v>
+      </c>
+      <c r="G17" s="14">
+        <v>5</v>
+      </c>
+      <c r="H17" s="14">
+        <v>0</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="164" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEFD7DC6-D894-4955-A688-AA60DAC7F516}"/>
+  <xr:revisionPtr revIDLastSave="178" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FCD2C57-C4C9-4E57-A910-77EC3879A6D0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -259,6 +259,9 @@
   </si>
   <si>
     <t>due to continuous classes felling tired.</t>
+  </si>
+  <si>
+    <t>tired.</t>
   </si>
 </sst>
 </file>
@@ -1594,26 +1597,50 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B18" s="14">
+        <v>360</v>
+      </c>
+      <c r="C18" s="14">
+        <v>0</v>
+      </c>
+      <c r="D18" s="14">
+        <v>180</v>
+      </c>
+      <c r="E18" s="14">
+        <v>150</v>
+      </c>
+      <c r="F18" s="14">
+        <v>300</v>
+      </c>
+      <c r="G18" s="14">
+        <v>6</v>
+      </c>
+      <c r="H18" s="14">
+        <v>20</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="178" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FCD2C57-C4C9-4E57-A910-77EC3879A6D0}"/>
+  <xr:revisionPtr revIDLastSave="192" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AFA0EF5-65DC-4695-84FD-D05FFEAFBD5F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -262,6 +262,9 @@
   </si>
   <si>
     <t>tired.</t>
+  </si>
+  <si>
+    <t>felling good.</t>
   </si>
 </sst>
 </file>
@@ -1643,26 +1646,50 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B19" s="14">
+        <v>400</v>
+      </c>
+      <c r="C19" s="14">
+        <v>20</v>
+      </c>
+      <c r="D19" s="14">
+        <v>180</v>
+      </c>
+      <c r="E19" s="14">
+        <v>120</v>
+      </c>
+      <c r="F19" s="14">
+        <v>50</v>
+      </c>
+      <c r="G19" s="14">
+        <v>1</v>
+      </c>
+      <c r="H19" s="14">
+        <v>30</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="192" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AFA0EF5-65DC-4695-84FD-D05FFEAFBD5F}"/>
+  <xr:revisionPtr revIDLastSave="204" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAE614E4-7280-490B-806F-F5F807973CB9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>felling good.</t>
+  </si>
+  <si>
+    <t>feelinag good and energetic because there is no class today.</t>
   </si>
 </sst>
 </file>
@@ -1691,27 +1694,51 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B20" s="14">
+        <v>420</v>
+      </c>
+      <c r="C20" s="14">
+        <v>50</v>
+      </c>
+      <c r="D20" s="14">
+        <v>120</v>
+      </c>
+      <c r="E20" s="14">
+        <v>90</v>
+      </c>
+      <c r="F20" s="14">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14">
+        <v>90</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>770</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>670</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,16 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="204" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAE614E4-7280-490B-806F-F5F807973CB9}"/>
+  <xr:revisionPtr revIDLastSave="232" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55454ACD-2B43-4DB5-9FF0-3FE3F57181F9}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -120,6 +123,9 @@
     <t xml:space="preserve">   Notes               - short free-text note (exams, illness, travel, anything explaining an unusual day)</t>
   </si>
   <si>
+    <t>5. GOOD PRACTICE</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Fill this in at the same time every day (e.g. before bed) so entries stay accurate.</t>
   </si>
   <si>
@@ -132,13 +138,22 @@
     <t>Name:</t>
   </si>
   <si>
+    <t>Vaibhav Dwivedi</t>
+  </si>
+  <si>
     <t>Registration No.:</t>
   </si>
   <si>
     <t>Course / Section:</t>
   </si>
   <si>
+    <t>CAP776/D2631</t>
+  </si>
+  <si>
     <t>Month:</t>
+  </si>
+  <si>
+    <t>August</t>
   </si>
   <si>
     <t>All durations in MINUTES. Yellow cells = enter your data. Row 6 is a sample — overwrite it. Rows 2-3: fill your details.</t>
@@ -196,18 +211,6 @@
   </si>
   <si>
     <t>Example row — replace with your own data. Felt a bit tired after evening class.</t>
-  </si>
-  <si>
-    <t>5. GOOD PRACTICE</t>
-  </si>
-  <si>
-    <t>Vaibhav Dwivedi</t>
-  </si>
-  <si>
-    <t>CAP776/D2631</t>
-  </si>
-  <si>
-    <t>August</t>
   </si>
   <si>
     <t>High</t>
@@ -268,6 +271,15 @@
   </si>
   <si>
     <t>feelinag good and energetic because there is no class today.</t>
+  </si>
+  <si>
+    <t>feel good.</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>feeling depressed</t>
   </si>
 </sst>
 </file>
@@ -889,17 +901,17 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
@@ -938,7 +950,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -956,15 +968,15 @@
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
       <c r="E2" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F2" s="20">
         <v>12600738</v>
@@ -973,24 +985,24 @@
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
       <c r="E3" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="G3" s="20"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -1008,46 +1020,46 @@
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1084,16 +1096,16 @@
         <v>555</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1130,10 +1142,10 @@
         <v>560</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M7" s="16" t="s">
         <v>57</v>
@@ -1228,7 +1240,7 @@
         <v>63</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N9" s="17" t="s">
         <v>64</v>
@@ -1268,13 +1280,13 @@
         <v>410</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L10" s="16" t="s">
         <v>63</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N10" s="17" t="s">
         <v>65</v>
@@ -1314,13 +1326,13 @@
         <v>570</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N11" s="17" t="s">
         <v>66</v>
@@ -1360,10 +1372,10 @@
         <v>570</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M12" s="16" t="s">
         <v>57</v>
@@ -1452,13 +1464,13 @@
         <v>450</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N14" s="17" t="s">
         <v>70</v>
@@ -1504,7 +1516,7 @@
         <v>63</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N15" s="17" t="s">
         <v>71</v>
@@ -1593,7 +1605,7 @@
         <v>61</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M17" s="16" t="s">
         <v>61</v>
@@ -1639,7 +1651,7 @@
         <v>61</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M18" s="16" t="s">
         <v>61</v>
@@ -1688,7 +1700,7 @@
         <v>63</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N19" s="17" t="s">
         <v>75</v>
@@ -1728,10 +1740,10 @@
         <v>670</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M20" s="16" t="s">
         <v>57</v>
@@ -1741,48 +1753,96 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B21" s="14">
+        <v>400</v>
+      </c>
+      <c r="C21" s="14">
+        <v>20</v>
+      </c>
+      <c r="D21" s="14">
+        <v>180</v>
+      </c>
+      <c r="E21" s="14">
+        <v>90</v>
+      </c>
+      <c r="F21" s="14">
+        <v>100</v>
+      </c>
+      <c r="G21" s="14">
+        <v>2</v>
+      </c>
+      <c r="H21" s="14">
+        <v>30</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>620</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B22" s="14">
+        <v>360</v>
+      </c>
+      <c r="C22" s="14">
+        <v>30</v>
+      </c>
+      <c r="D22" s="14">
+        <v>120</v>
+      </c>
+      <c r="E22" s="14">
+        <v>120</v>
+      </c>
+      <c r="F22" s="14">
+        <v>300</v>
+      </c>
+      <c r="G22" s="14">
+        <v>6</v>
+      </c>
+      <c r="H22" s="14">
+        <v>50</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="232" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55454ACD-2B43-4DB5-9FF0-3FE3F57181F9}"/>
+  <xr:revisionPtr revIDLastSave="245" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{739129DB-33BA-453D-946D-6571B4D93971}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -280,6 +280,9 @@
   </si>
   <si>
     <t>feeling depressed</t>
+  </si>
+  <si>
+    <t>just living life.</t>
   </si>
 </sst>
 </file>
@@ -1845,26 +1848,50 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B23" s="14">
+        <v>400</v>
+      </c>
+      <c r="C23" s="14">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
+        <v>150</v>
+      </c>
+      <c r="E23" s="14">
+        <v>90</v>
+      </c>
+      <c r="F23" s="14">
+        <v>400</v>
+      </c>
+      <c r="G23" s="14">
+        <v>8</v>
+      </c>
+      <c r="H23" s="14">
+        <v>0</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="245" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{739129DB-33BA-453D-946D-6571B4D93971}"/>
+  <xr:revisionPtr revIDLastSave="257" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{054B810B-7802-4824-BD3E-8CFF075EEFFD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -283,6 +283,9 @@
   </si>
   <si>
     <t>just living life.</t>
+  </si>
+  <si>
+    <t>just felling good in comparison to other day's.</t>
   </si>
 </sst>
 </file>
@@ -1893,27 +1896,51 @@
         <v>80</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+    <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B24" s="14">
+        <v>360</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>180</v>
+      </c>
+      <c r="E24" s="14">
+        <v>120</v>
+      </c>
+      <c r="F24" s="14">
+        <v>250</v>
+      </c>
+      <c r="G24" s="14">
+        <v>5</v>
+      </c>
+      <c r="H24" s="14">
+        <v>20</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="257" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{054B810B-7802-4824-BD3E-8CFF075EEFFD}"/>
+  <xr:revisionPtr revIDLastSave="300" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F8593A7-3644-4A98-8965-7BC12E4567CE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -287,6 +287,15 @@
   <si>
     <t>just felling good in comparison to other day's.</t>
   </si>
+  <si>
+    <t>good.</t>
+  </si>
+  <si>
+    <t>satisfied</t>
+  </si>
+  <si>
+    <t>depressed.</t>
+  </si>
 </sst>
 </file>
 
@@ -397,7 +406,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -420,11 +429,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -468,6 +488,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1943,70 +1966,140 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B25" s="14">
+        <v>360</v>
+      </c>
+      <c r="C25" s="14">
+        <v>20</v>
+      </c>
+      <c r="D25" s="14">
+        <v>180</v>
+      </c>
+      <c r="E25" s="14">
+        <v>90</v>
+      </c>
+      <c r="F25" s="14">
+        <v>300</v>
+      </c>
+      <c r="G25" s="14">
+        <v>6</v>
+      </c>
+      <c r="H25" s="14">
+        <v>30</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
+        <v>460</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>63</v>
+      </c>
       <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+      <c r="N25" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B26" s="14">
+        <v>400</v>
+      </c>
+      <c r="C26" s="14">
+        <v>30</v>
+      </c>
+      <c r="D26" s="14">
+        <v>150</v>
+      </c>
+      <c r="E26" s="14">
+        <v>90</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>60</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>710</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L26" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="M26" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B27" s="14">
+        <v>500</v>
+      </c>
+      <c r="C27" s="14">
+        <v>60</v>
+      </c>
+      <c r="D27" s="14">
+        <v>120</v>
+      </c>
+      <c r="E27" s="14">
+        <v>90</v>
+      </c>
+      <c r="F27" s="14">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14">
+        <v>30</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L27" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>
@@ -10255,11 +10348,11 @@
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L25 L28:L401 M28" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M25 M27 M29:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="300" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F8593A7-3644-4A98-8965-7BC12E4567CE}"/>
+  <xr:revisionPtr revIDLastSave="328" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52F63EB6-909D-453D-85B4-B0B6F13420FA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -296,6 +296,9 @@
   <si>
     <t>depressed.</t>
   </si>
+  <si>
+    <t>suffering from fever.</t>
+  </si>
 </sst>
 </file>
 
@@ -485,12 +488,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -978,74 +981,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="21">
         <v>12600738</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -2045,10 +2048,10 @@
       <c r="K26" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="L26" s="21" t="s">
+      <c r="L26" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="M26" s="21" t="s">
+      <c r="M26" s="18" t="s">
         <v>55</v>
       </c>
       <c r="N26" s="17" t="s">
@@ -2091,7 +2094,7 @@
       <c r="K27" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="L27" s="21" t="s">
+      <c r="L27" s="18" t="s">
         <v>83</v>
       </c>
       <c r="M27" s="16" t="s">
@@ -2102,48 +2105,96 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B28" s="14">
+        <v>700</v>
+      </c>
+      <c r="C28" s="14">
+        <v>0</v>
+      </c>
+      <c r="D28" s="14">
+        <v>0</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
+      </c>
+      <c r="F28" s="14">
+        <v>100</v>
+      </c>
+      <c r="G28" s="14">
+        <v>2</v>
+      </c>
+      <c r="H28" s="14">
+        <v>0</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B29" s="14">
+        <v>800</v>
+      </c>
+      <c r="C29" s="14">
+        <v>0</v>
+      </c>
+      <c r="D29" s="14">
+        <v>60</v>
+      </c>
+      <c r="E29" s="14">
+        <v>30</v>
+      </c>
+      <c r="F29" s="14">
+        <v>150</v>
+      </c>
+      <c r="G29" s="14">
+        <v>3</v>
+      </c>
+      <c r="H29" s="14">
+        <v>0</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>
@@ -10348,11 +10399,11 @@
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L25 L28:L401 M28" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L25 L28:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M25 M27 M29:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M25 M27:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/vaibhav.xlsx
+++ b/vaibhav.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9585A7B6EA7D5F67/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vaibhav dwivedi\OneDrive\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="328" documentId="8_{B172051D-E546-4EF9-A80D-71C24288056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52F63EB6-909D-453D-85B4-B0B6F13420FA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32390369-A2B4-4C7E-AFD8-37A2658EEB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -298,6 +298,9 @@
   </si>
   <si>
     <t>suffering from fever.</t>
+  </si>
+  <si>
+    <t>feeling happy today because no class today.</t>
   </si>
 </sst>
 </file>
@@ -592,10 +595,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2197,92 +2196,188 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B30" s="14">
+        <v>550</v>
+      </c>
+      <c r="C30" s="14">
+        <v>0</v>
+      </c>
+      <c r="D30" s="14">
+        <v>90</v>
+      </c>
+      <c r="E30" s="14">
+        <v>60</v>
+      </c>
+      <c r="F30" s="14">
+        <v>400</v>
+      </c>
+      <c r="G30" s="14">
+        <v>8</v>
+      </c>
+      <c r="H30" s="14">
+        <v>20</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>320</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B31" s="14">
+        <v>480</v>
+      </c>
+      <c r="C31" s="14">
+        <v>20</v>
+      </c>
+      <c r="D31" s="14">
+        <v>90</v>
+      </c>
+      <c r="E31" s="14">
+        <v>60</v>
+      </c>
+      <c r="F31" s="14">
+        <v>250</v>
+      </c>
+      <c r="G31" s="14">
+        <v>5</v>
+      </c>
+      <c r="H31" s="14">
+        <v>30</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B32" s="14">
+        <v>480</v>
+      </c>
+      <c r="C32" s="14">
+        <v>30</v>
+      </c>
+      <c r="D32" s="14">
+        <v>120</v>
+      </c>
+      <c r="E32" s="14">
+        <v>90</v>
+      </c>
+      <c r="F32" s="14">
+        <v>300</v>
+      </c>
+      <c r="G32" s="14">
+        <v>6</v>
+      </c>
+      <c r="H32" s="14">
+        <v>30</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+        <v>390</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B33" s="14">
+        <v>540</v>
+      </c>
+      <c r="C33" s="14">
+        <v>50</v>
+      </c>
+      <c r="D33" s="14">
+        <v>120</v>
+      </c>
+      <c r="E33" s="14">
+        <v>90</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>30</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>610</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>
